--- a/artfynd/A 24130-2020 artfynd.xlsx
+++ b/artfynd/A 24130-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +791,946 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123420419</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90955</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>601413</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6865769</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2024_2690</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123420411</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78414</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>601326</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6865746</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2024_2701</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>kelohögstubbe med brandspår</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123420410</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79358</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>601327</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6865747</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2024_2702</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>kelohögstubbe</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123420413</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80726</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>601442</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6865727</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2024_2697</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>kelostubbe</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123420415</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79387</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>601439</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6865751</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2024_2695</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>tallstubbe</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123420418</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78769</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>601382</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6865738</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2024_2693</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123420409</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79387</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bodåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>601327</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6865747</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2024_2703</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>kelohögstubbe</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24130-2020 artfynd.xlsx
+++ b/artfynd/A 24130-2020 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420419</v>
+        <v>123420409</v>
       </c>
       <c r="B3" t="n">
-        <v>90955</v>
+        <v>79389</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601413</v>
+        <v>601327</v>
       </c>
       <c r="R3" t="n">
-        <v>6865769</v>
+        <v>6865747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2690</t>
+          <t>2024_2703</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420411</v>
+        <v>123420419</v>
       </c>
       <c r="B4" t="n">
-        <v>78414</v>
+        <v>90957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,31 +945,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601326</v>
+        <v>601413</v>
       </c>
       <c r="R4" t="n">
-        <v>6865746</v>
+        <v>6865769</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2701</t>
+          <t>2024_2690</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>kelohögstubbe med brandspår</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,10 +1064,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420410</v>
+        <v>123420411</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>78416</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,21 +1080,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601327</v>
+        <v>601326</v>
       </c>
       <c r="R5" t="n">
-        <v>6865747</v>
+        <v>6865746</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2702</t>
+          <t>2024_2701</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>kelohögstubbe med brandspår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420413</v>
+        <v>123420418</v>
       </c>
       <c r="B6" t="n">
-        <v>80726</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,31 +1215,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601442</v>
+        <v>601382</v>
       </c>
       <c r="R6" t="n">
-        <v>6865727</v>
+        <v>6865738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2697</t>
+          <t>2024_2693</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1298,12 +1298,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>kelostubbe</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1323,7 +1318,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1334,10 +1329,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123420415</v>
+        <v>123420413</v>
       </c>
       <c r="B7" t="n">
-        <v>79387</v>
+        <v>80728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1350,31 +1345,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1383,10 +1378,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601439</v>
+        <v>601442</v>
       </c>
       <c r="R7" t="n">
-        <v>6865751</v>
+        <v>6865727</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1413,7 +1408,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2695</t>
+          <t>2024_2697</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1423,7 +1418,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1433,12 +1428,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>kelostubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1469,10 +1464,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123420418</v>
+        <v>123420410</v>
       </c>
       <c r="B8" t="n">
-        <v>78769</v>
+        <v>79360</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1485,26 +1480,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1518,10 +1513,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601382</v>
+        <v>601327</v>
       </c>
       <c r="R8" t="n">
-        <v>6865738</v>
+        <v>6865747</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1548,7 +1543,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_2693</t>
+          <t>2024_2702</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1558,7 +1553,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1568,7 +1563,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123420409</v>
+        <v>123420415</v>
       </c>
       <c r="B9" t="n">
-        <v>79387</v>
+        <v>79389</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601327</v>
+        <v>601439</v>
       </c>
       <c r="R9" t="n">
-        <v>6865747</v>
+        <v>6865751</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_2703</t>
+          <t>2024_2695</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 24130-2020 artfynd.xlsx
+++ b/artfynd/A 24130-2020 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420409</v>
+        <v>123420418</v>
       </c>
       <c r="B3" t="n">
-        <v>79389</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,31 +810,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601327</v>
+        <v>601382</v>
       </c>
       <c r="R3" t="n">
-        <v>6865747</v>
+        <v>6865738</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2703</t>
+          <t>2024_2693</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>kelohögstubbe</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +913,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -929,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420419</v>
+        <v>123420415</v>
       </c>
       <c r="B4" t="n">
-        <v>90957</v>
+        <v>79390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,31 +940,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -978,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601413</v>
+        <v>601439</v>
       </c>
       <c r="R4" t="n">
-        <v>6865769</v>
+        <v>6865751</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1003,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2690</t>
+          <t>2024_2695</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1018,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,12 +1023,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420411</v>
+        <v>123420419</v>
       </c>
       <c r="B5" t="n">
-        <v>78416</v>
+        <v>90963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,31 +1075,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1113,10 +1108,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601326</v>
+        <v>601413</v>
       </c>
       <c r="R5" t="n">
-        <v>6865746</v>
+        <v>6865769</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1138,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2701</t>
+          <t>2024_2690</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1153,7 +1148,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1163,12 +1158,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>kelohögstubbe med brandspår</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,10 +1194,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420418</v>
+        <v>123420411</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>78417</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,26 +1210,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1248,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601382</v>
+        <v>601326</v>
       </c>
       <c r="R6" t="n">
-        <v>6865738</v>
+        <v>6865746</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1273,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2693</t>
+          <t>2024_2701</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1288,7 +1283,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1298,7 +1293,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>kelohögstubbe med brandspår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1332,7 +1332,7 @@
         <v>123420413</v>
       </c>
       <c r="B7" t="n">
-        <v>80728</v>
+        <v>80729</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123420410</v>
+        <v>123420409</v>
       </c>
       <c r="B8" t="n">
-        <v>79360</v>
+        <v>79390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1480,31 +1480,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_2702</t>
+          <t>2024_2703</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123420415</v>
+        <v>123420410</v>
       </c>
       <c r="B9" t="n">
-        <v>79389</v>
+        <v>79361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1615,31 +1615,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601439</v>
+        <v>601327</v>
       </c>
       <c r="R9" t="n">
-        <v>6865751</v>
+        <v>6865747</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_2695</t>
+          <t>2024_2702</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 24130-2020 artfynd.xlsx
+++ b/artfynd/A 24130-2020 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>123420418</v>
       </c>
       <c r="B3" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420415</v>
+        <v>123420413</v>
       </c>
       <c r="B4" t="n">
-        <v>79390</v>
+        <v>80732</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,31 +940,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601439</v>
+        <v>601442</v>
       </c>
       <c r="R4" t="n">
-        <v>6865751</v>
+        <v>6865727</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2695</t>
+          <t>2024_2697</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>kelostubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420419</v>
+        <v>123420411</v>
       </c>
       <c r="B5" t="n">
-        <v>90963</v>
+        <v>78420</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,31 +1075,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601413</v>
+        <v>601326</v>
       </c>
       <c r="R5" t="n">
-        <v>6865769</v>
+        <v>6865746</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2690</t>
+          <t>2024_2701</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>kelohögstubbe med brandspår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1194,10 +1194,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420411</v>
+        <v>123420409</v>
       </c>
       <c r="B6" t="n">
-        <v>78417</v>
+        <v>79393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,31 +1210,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601326</v>
+        <v>601327</v>
       </c>
       <c r="R6" t="n">
-        <v>6865746</v>
+        <v>6865747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2701</t>
+          <t>2024_2703</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>kelohögstubbe med brandspår</t>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,10 +1329,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123420413</v>
+        <v>123420415</v>
       </c>
       <c r="B7" t="n">
-        <v>80729</v>
+        <v>79393</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1345,31 +1345,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601442</v>
+        <v>601439</v>
       </c>
       <c r="R7" t="n">
-        <v>6865727</v>
+        <v>6865751</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2697</t>
+          <t>2024_2695</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>kelostubbe</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123420409</v>
+        <v>123420410</v>
       </c>
       <c r="B8" t="n">
-        <v>79390</v>
+        <v>79364</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1480,31 +1480,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_2703</t>
+          <t>2024_2702</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123420410</v>
+        <v>123420419</v>
       </c>
       <c r="B9" t="n">
-        <v>79361</v>
+        <v>90966</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1615,31 +1615,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601327</v>
+        <v>601413</v>
       </c>
       <c r="R9" t="n">
-        <v>6865747</v>
+        <v>6865769</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_2702</t>
+          <t>2024_2690</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 24130-2020 artfynd.xlsx
+++ b/artfynd/A 24130-2020 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>123420418</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420413</v>
+        <v>123420410</v>
       </c>
       <c r="B4" t="n">
-        <v>80732</v>
+        <v>79370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,31 +940,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601442</v>
+        <v>601327</v>
       </c>
       <c r="R4" t="n">
-        <v>6865727</v>
+        <v>6865747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2697</t>
+          <t>2024_2702</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>kelostubbe</t>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,7 +1062,7 @@
         <v>123420411</v>
       </c>
       <c r="B5" t="n">
-        <v>78420</v>
+        <v>78426</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420409</v>
+        <v>123420419</v>
       </c>
       <c r="B6" t="n">
-        <v>79393</v>
+        <v>90983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601327</v>
+        <v>601413</v>
       </c>
       <c r="R6" t="n">
-        <v>6865747</v>
+        <v>6865769</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2703</t>
+          <t>2024_2690</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,10 +1329,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123420415</v>
+        <v>123420409</v>
       </c>
       <c r="B7" t="n">
-        <v>79393</v>
+        <v>79399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601439</v>
+        <v>601327</v>
       </c>
       <c r="R7" t="n">
-        <v>6865751</v>
+        <v>6865747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2695</t>
+          <t>2024_2703</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123420410</v>
+        <v>123420415</v>
       </c>
       <c r="B8" t="n">
-        <v>79364</v>
+        <v>79399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1480,31 +1480,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601327</v>
+        <v>601439</v>
       </c>
       <c r="R8" t="n">
-        <v>6865747</v>
+        <v>6865751</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_2702</t>
+          <t>2024_2695</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123420419</v>
+        <v>123420413</v>
       </c>
       <c r="B9" t="n">
-        <v>90966</v>
+        <v>80734</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1615,31 +1615,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601413</v>
+        <v>601442</v>
       </c>
       <c r="R9" t="n">
-        <v>6865769</v>
+        <v>6865727</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_2690</t>
+          <t>2024_2697</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>kelostubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 24130-2020 artfynd.xlsx
+++ b/artfynd/A 24130-2020 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420418</v>
+        <v>123420409</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>79404</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,31 +810,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601382</v>
+        <v>601327</v>
       </c>
       <c r="R3" t="n">
-        <v>6865738</v>
+        <v>6865747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2693</t>
+          <t>2024_2703</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +893,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +918,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -924,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420410</v>
+        <v>123420413</v>
       </c>
       <c r="B4" t="n">
-        <v>79370</v>
+        <v>80739</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,31 +945,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601327</v>
+        <v>601442</v>
       </c>
       <c r="R4" t="n">
-        <v>6865747</v>
+        <v>6865727</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1008,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2702</t>
+          <t>2024_2697</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1013,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,12 +1028,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>kelostubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,7 +1067,7 @@
         <v>123420411</v>
       </c>
       <c r="B5" t="n">
-        <v>78426</v>
+        <v>78431</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1197,7 +1202,7 @@
         <v>123420419</v>
       </c>
       <c r="B6" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1329,10 +1334,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123420409</v>
+        <v>123420415</v>
       </c>
       <c r="B7" t="n">
-        <v>79399</v>
+        <v>79404</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1364,7 +1369,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1378,10 +1383,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601327</v>
+        <v>601439</v>
       </c>
       <c r="R7" t="n">
-        <v>6865747</v>
+        <v>6865751</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,7 +1413,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2703</t>
+          <t>2024_2695</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1418,7 +1423,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1428,12 +1433,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1464,10 +1469,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123420415</v>
+        <v>123420410</v>
       </c>
       <c r="B8" t="n">
-        <v>79399</v>
+        <v>79375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1480,31 +1485,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1513,10 +1518,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601439</v>
+        <v>601327</v>
       </c>
       <c r="R8" t="n">
-        <v>6865751</v>
+        <v>6865747</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1543,7 +1548,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_2695</t>
+          <t>2024_2702</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1553,7 +1558,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1563,12 +1568,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,10 +1604,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123420413</v>
+        <v>123420418</v>
       </c>
       <c r="B9" t="n">
-        <v>80734</v>
+        <v>78786</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1615,31 +1620,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601442</v>
+        <v>601382</v>
       </c>
       <c r="R9" t="n">
-        <v>6865727</v>
+        <v>6865738</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,7 +1683,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_2697</t>
+          <t>2024_2693</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1688,7 +1693,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1698,12 +1703,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>kelostubbe</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 24130-2020 artfynd.xlsx
+++ b/artfynd/A 24130-2020 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420409</v>
+        <v>123420419</v>
       </c>
       <c r="B3" t="n">
-        <v>79404</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601327</v>
+        <v>601413</v>
       </c>
       <c r="R3" t="n">
-        <v>6865747</v>
+        <v>6865769</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2703</t>
+          <t>2024_2690</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420413</v>
+        <v>123420415</v>
       </c>
       <c r="B4" t="n">
-        <v>80739</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,31 +945,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601442</v>
+        <v>601439</v>
       </c>
       <c r="R4" t="n">
-        <v>6865727</v>
+        <v>6865751</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2697</t>
+          <t>2024_2695</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>kelostubbe</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,10 +1064,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420411</v>
+        <v>123420418</v>
       </c>
       <c r="B5" t="n">
-        <v>78431</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,26 +1080,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601326</v>
+        <v>601382</v>
       </c>
       <c r="R5" t="n">
-        <v>6865746</v>
+        <v>6865738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2701</t>
+          <t>2024_2693</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1163,12 +1163,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>kelohögstubbe med brandspår</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1188,7 +1183,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1199,10 +1194,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420419</v>
+        <v>123420409</v>
       </c>
       <c r="B6" t="n">
-        <v>90988</v>
+        <v>79406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,21 +1210,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1239,7 +1234,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1248,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601413</v>
+        <v>601327</v>
       </c>
       <c r="R6" t="n">
-        <v>6865769</v>
+        <v>6865747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1273,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2690</t>
+          <t>2024_2703</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1288,7 +1283,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1298,12 +1293,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,10 +1329,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123420415</v>
+        <v>123420411</v>
       </c>
       <c r="B7" t="n">
-        <v>79404</v>
+        <v>78433</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1350,31 +1345,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1383,10 +1378,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601439</v>
+        <v>601326</v>
       </c>
       <c r="R7" t="n">
-        <v>6865751</v>
+        <v>6865746</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1413,7 +1408,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2695</t>
+          <t>2024_2701</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1423,7 +1418,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1433,12 +1428,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>kelohögstubbe med brandspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1472,7 +1467,7 @@
         <v>123420410</v>
       </c>
       <c r="B8" t="n">
-        <v>79375</v>
+        <v>79377</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1604,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123420418</v>
+        <v>123420413</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>80741</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1620,31 +1615,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601382</v>
+        <v>601442</v>
       </c>
       <c r="R9" t="n">
-        <v>6865738</v>
+        <v>6865727</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1683,7 +1678,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_2693</t>
+          <t>2024_2697</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1693,7 +1688,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1703,7 +1698,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>kelostubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 24130-2020 artfynd.xlsx
+++ b/artfynd/A 24130-2020 artfynd.xlsx
@@ -1064,10 +1064,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420418</v>
+        <v>123420409</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,31 +1080,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601382</v>
+        <v>601327</v>
       </c>
       <c r="R5" t="n">
-        <v>6865738</v>
+        <v>6865747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2693</t>
+          <t>2024_2703</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1163,7 +1163,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,7 +1188,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1194,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420409</v>
+        <v>123420418</v>
       </c>
       <c r="B6" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,31 +1215,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1243,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601327</v>
+        <v>601382</v>
       </c>
       <c r="R6" t="n">
-        <v>6865747</v>
+        <v>6865738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1273,7 +1278,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2703</t>
+          <t>2024_2693</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1283,7 +1288,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1293,12 +1298,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>kelohögstubbe</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 24130-2020 artfynd.xlsx
+++ b/artfynd/A 24130-2020 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420419</v>
+        <v>123420418</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,31 +810,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601413</v>
+        <v>601382</v>
       </c>
       <c r="R3" t="n">
-        <v>6865769</v>
+        <v>6865738</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2690</t>
+          <t>2024_2693</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +913,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1064,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420409</v>
+        <v>123420413</v>
       </c>
       <c r="B5" t="n">
-        <v>79406</v>
+        <v>80741</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,31 +1075,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1113,10 +1108,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601327</v>
+        <v>601442</v>
       </c>
       <c r="R5" t="n">
-        <v>6865747</v>
+        <v>6865727</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1138,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2703</t>
+          <t>2024_2697</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1153,7 +1148,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1163,12 +1158,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>kelostubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,10 +1194,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420418</v>
+        <v>123420409</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,31 +1210,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1248,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601382</v>
+        <v>601327</v>
       </c>
       <c r="R6" t="n">
-        <v>6865738</v>
+        <v>6865747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1273,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2693</t>
+          <t>2024_2703</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1288,7 +1283,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1298,7 +1293,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123420410</v>
+        <v>123420419</v>
       </c>
       <c r="B8" t="n">
-        <v>79377</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1480,31 +1480,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601327</v>
+        <v>601413</v>
       </c>
       <c r="R8" t="n">
-        <v>6865747</v>
+        <v>6865769</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_2702</t>
+          <t>2024_2690</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123420413</v>
+        <v>123420410</v>
       </c>
       <c r="B9" t="n">
-        <v>80741</v>
+        <v>79377</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1615,31 +1615,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601442</v>
+        <v>601327</v>
       </c>
       <c r="R9" t="n">
-        <v>6865727</v>
+        <v>6865747</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_2697</t>
+          <t>2024_2702</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>kelostubbe</t>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 24130-2020 artfynd.xlsx
+++ b/artfynd/A 24130-2020 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420418</v>
+        <v>123420415</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601382</v>
+        <v>601439</v>
       </c>
       <c r="R3" t="n">
-        <v>6865738</v>
+        <v>6865751</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2693</t>
+          <t>2024_2695</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +893,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +918,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -924,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420415</v>
+        <v>123420410</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>79377</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,31 +945,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -973,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601439</v>
+        <v>601327</v>
       </c>
       <c r="R4" t="n">
-        <v>6865751</v>
+        <v>6865747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1008,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2695</t>
+          <t>2024_2702</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1013,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,12 +1028,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,10 +1064,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420413</v>
+        <v>123420409</v>
       </c>
       <c r="B5" t="n">
-        <v>80741</v>
+        <v>79406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,31 +1080,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1108,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601442</v>
+        <v>601327</v>
       </c>
       <c r="R5" t="n">
-        <v>6865727</v>
+        <v>6865747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,7 +1143,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2697</t>
+          <t>2024_2703</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1148,7 +1153,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1158,12 +1163,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>kelostubbe</t>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1194,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420409</v>
+        <v>123420418</v>
       </c>
       <c r="B6" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,31 +1215,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1243,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601327</v>
+        <v>601382</v>
       </c>
       <c r="R6" t="n">
-        <v>6865747</v>
+        <v>6865738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1273,7 +1278,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2703</t>
+          <t>2024_2693</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1283,7 +1288,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1293,12 +1298,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>kelohögstubbe</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123420419</v>
+        <v>123420413</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>80741</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1480,31 +1480,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601413</v>
+        <v>601442</v>
       </c>
       <c r="R8" t="n">
-        <v>6865769</v>
+        <v>6865727</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_2690</t>
+          <t>2024_2697</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>kelostubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123420410</v>
+        <v>123420419</v>
       </c>
       <c r="B9" t="n">
-        <v>79377</v>
+        <v>90990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1615,31 +1615,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601327</v>
+        <v>601413</v>
       </c>
       <c r="R9" t="n">
-        <v>6865747</v>
+        <v>6865769</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_2702</t>
+          <t>2024_2690</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 24130-2020 artfynd.xlsx
+++ b/artfynd/A 24130-2020 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420415</v>
+        <v>123420419</v>
       </c>
       <c r="B3" t="n">
-        <v>79406</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,31 +810,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601439</v>
+        <v>601413</v>
       </c>
       <c r="R3" t="n">
-        <v>6865751</v>
+        <v>6865769</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2695</t>
+          <t>2024_2690</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420410</v>
+        <v>123420411</v>
       </c>
       <c r="B4" t="n">
-        <v>79377</v>
+        <v>78433</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,21 +945,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601327</v>
+        <v>601326</v>
       </c>
       <c r="R4" t="n">
-        <v>6865747</v>
+        <v>6865746</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2702</t>
+          <t>2024_2701</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>kelohögstubbe med brandspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,10 +1064,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420409</v>
+        <v>123420410</v>
       </c>
       <c r="B5" t="n">
-        <v>79406</v>
+        <v>79377</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,31 +1080,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2703</t>
+          <t>2024_2702</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1199,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420418</v>
+        <v>123420415</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,21 +1215,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601382</v>
+        <v>601439</v>
       </c>
       <c r="R6" t="n">
-        <v>6865738</v>
+        <v>6865751</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2693</t>
+          <t>2024_2695</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1298,7 +1298,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,7 +1323,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1329,10 +1334,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123420411</v>
+        <v>123420413</v>
       </c>
       <c r="B7" t="n">
-        <v>78433</v>
+        <v>80741</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1345,31 +1350,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1378,10 +1383,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601326</v>
+        <v>601442</v>
       </c>
       <c r="R7" t="n">
-        <v>6865746</v>
+        <v>6865727</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,7 +1413,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2701</t>
+          <t>2024_2697</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1418,7 +1423,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1428,12 +1433,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>kelohögstubbe med brandspår</t>
+          <t>kelostubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1464,10 +1469,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123420413</v>
+        <v>123420418</v>
       </c>
       <c r="B8" t="n">
-        <v>80741</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1480,31 +1485,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1513,10 +1518,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601442</v>
+        <v>601382</v>
       </c>
       <c r="R8" t="n">
-        <v>6865727</v>
+        <v>6865738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1543,7 +1548,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_2697</t>
+          <t>2024_2693</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1553,7 +1558,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1563,12 +1568,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>kelostubbe</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123420419</v>
+        <v>123420409</v>
       </c>
       <c r="B9" t="n">
-        <v>90990</v>
+        <v>79406</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1615,21 +1615,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601413</v>
+        <v>601327</v>
       </c>
       <c r="R9" t="n">
-        <v>6865769</v>
+        <v>6865747</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_2690</t>
+          <t>2024_2703</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 24130-2020 artfynd.xlsx
+++ b/artfynd/A 24130-2020 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420419</v>
+        <v>123420411</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>78433</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,31 +810,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601413</v>
+        <v>601326</v>
       </c>
       <c r="R3" t="n">
-        <v>6865769</v>
+        <v>6865746</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2690</t>
+          <t>2024_2701</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>kelohögstubbe med brandspår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420411</v>
+        <v>123420410</v>
       </c>
       <c r="B4" t="n">
-        <v>78433</v>
+        <v>79377</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,21 +945,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601326</v>
+        <v>601327</v>
       </c>
       <c r="R4" t="n">
-        <v>6865746</v>
+        <v>6865747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2701</t>
+          <t>2024_2702</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>kelohögstubbe med brandspår</t>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,10 +1064,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420410</v>
+        <v>123420419</v>
       </c>
       <c r="B5" t="n">
-        <v>79377</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,31 +1080,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601327</v>
+        <v>601413</v>
       </c>
       <c r="R5" t="n">
-        <v>6865747</v>
+        <v>6865769</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2702</t>
+          <t>2024_2690</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420415</v>
+        <v>123420413</v>
       </c>
       <c r="B6" t="n">
-        <v>79406</v>
+        <v>80741</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,31 +1215,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601439</v>
+        <v>601442</v>
       </c>
       <c r="R6" t="n">
-        <v>6865751</v>
+        <v>6865727</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2695</t>
+          <t>2024_2697</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>kelostubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,10 +1334,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123420413</v>
+        <v>123420418</v>
       </c>
       <c r="B7" t="n">
-        <v>80741</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1350,31 +1350,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601442</v>
+        <v>601382</v>
       </c>
       <c r="R7" t="n">
-        <v>6865727</v>
+        <v>6865738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2697</t>
+          <t>2024_2693</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1433,12 +1433,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>kelostubbe</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1458,7 +1453,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1469,10 +1464,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123420418</v>
+        <v>123420415</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1485,21 +1480,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1509,7 +1504,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1518,10 +1513,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601382</v>
+        <v>601439</v>
       </c>
       <c r="R8" t="n">
-        <v>6865738</v>
+        <v>6865751</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1548,7 +1543,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_2693</t>
+          <t>2024_2695</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1558,7 +1553,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1568,7 +1563,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 24130-2020 artfynd.xlsx
+++ b/artfynd/A 24130-2020 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123420411</v>
+        <v>123420413</v>
       </c>
       <c r="B3" t="n">
-        <v>78433</v>
+        <v>80741</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,31 +810,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601326</v>
+        <v>601442</v>
       </c>
       <c r="R3" t="n">
-        <v>6865746</v>
+        <v>6865727</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2701</t>
+          <t>2024_2697</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>kelohögstubbe med brandspår</t>
+          <t>kelostubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420410</v>
+        <v>123420415</v>
       </c>
       <c r="B4" t="n">
-        <v>79377</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,31 +945,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601327</v>
+        <v>601439</v>
       </c>
       <c r="R4" t="n">
-        <v>6865747</v>
+        <v>6865751</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2702</t>
+          <t>2024_2695</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,10 +1064,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123420419</v>
+        <v>123420410</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>79377</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,31 +1080,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601413</v>
+        <v>601327</v>
       </c>
       <c r="R5" t="n">
-        <v>6865769</v>
+        <v>6865747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_2690</t>
+          <t>2024_2702</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123420413</v>
+        <v>123420418</v>
       </c>
       <c r="B6" t="n">
-        <v>80741</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,31 +1215,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601442</v>
+        <v>601382</v>
       </c>
       <c r="R6" t="n">
-        <v>6865727</v>
+        <v>6865738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_2697</t>
+          <t>2024_2693</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1298,12 +1298,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>kelostubbe</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1323,7 +1318,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1334,10 +1329,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123420418</v>
+        <v>123420419</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1350,31 +1345,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1383,10 +1378,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601382</v>
+        <v>601413</v>
       </c>
       <c r="R7" t="n">
-        <v>6865738</v>
+        <v>6865769</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1413,7 +1408,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_2693</t>
+          <t>2024_2690</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1423,7 +1418,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1433,7 +1428,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1464,7 +1464,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123420415</v>
+        <v>123420409</v>
       </c>
       <c r="B8" t="n">
         <v>79406</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601439</v>
+        <v>601327</v>
       </c>
       <c r="R8" t="n">
-        <v>6865751</v>
+        <v>6865747</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_2695</t>
+          <t>2024_2703</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123420409</v>
+        <v>123420411</v>
       </c>
       <c r="B9" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1615,31 +1615,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601327</v>
+        <v>601326</v>
       </c>
       <c r="R9" t="n">
-        <v>6865747</v>
+        <v>6865746</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_2703</t>
+          <t>2024_2701</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>kelohögstubbe</t>
+          <t>kelohögstubbe med brandspår</t>
         </is>
       </c>
       <c r="AD9" t="b">
